--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/06,07,26 Останкино КИ/дв 06,07,26 бррсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/06,07,26 Останкино КИ/дв 06,07,26 бррсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\06,07,26 Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F197A6-1B99-4F7F-A2CA-B9BBB7521781}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCCEB82-10FD-47C4-8124-7933DB0ABCBA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$109</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="153">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -500,6 +500,30 @@
   </si>
   <si>
     <t>13,07,</t>
+  </si>
+  <si>
+    <t>7647  ХОЧУ ВЕТЧ. ИЗ СВИН.ОТРУБА с/н мгс 1/100</t>
+  </si>
+  <si>
+    <t>7299  НАБОР ДЛЯ ПИЦЦЫ Папа Может с/к в/у</t>
+  </si>
+  <si>
+    <t>7651  ХОЧУ ВЕТЧ. МРАМОР. ПМ с/н мгс 1/100_Л11</t>
+  </si>
+  <si>
+    <t>новинка</t>
+  </si>
+  <si>
+    <t>ротация на 1001061977613,АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10</t>
+  </si>
+  <si>
+    <t>ротация на 1001062507616,ЭКСТРА Папа может с/к с/н в/у 1/100_Л10</t>
+  </si>
+  <si>
+    <t>ротация на 1001304197608,СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
+  </si>
+  <si>
+    <t>плюсом 5 дней</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1326,7 @@
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>14253</v>
+        <v>15303</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1333,7 +1357,7 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="4">
         <f>SUM(AD6:AD500)</f>
-        <v>5612.2400000000007</v>
+        <v>5762.2400000000007</v>
       </c>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
@@ -1544,7 +1568,9 @@
       <c r="AB7" s="1">
         <v>2.7652000000000001</v>
       </c>
-      <c r="AC7" s="1"/>
+      <c r="AC7" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="AD7" s="1">
         <f t="shared" ref="AD7:AD70" si="7">G7*T7</f>
         <v>25</v>
@@ -1655,7 +1681,9 @@
       <c r="AB8" s="1">
         <v>30.8</v>
       </c>
-      <c r="AC8" s="1"/>
+      <c r="AC8" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="AD8" s="1">
         <f t="shared" si="7"/>
         <v>84</v>
@@ -1873,7 +1901,9 @@
       <c r="AB10" s="1">
         <v>1.2904</v>
       </c>
-      <c r="AC10" s="1"/>
+      <c r="AC10" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="AD10" s="1">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -2191,7 +2221,9 @@
       <c r="AB13" s="1">
         <v>16.8</v>
       </c>
-      <c r="AC13" s="1"/>
+      <c r="AC13" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="AD13" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -2508,7 +2540,9 @@
       <c r="AB16" s="1">
         <v>35.6</v>
       </c>
-      <c r="AC16" s="1"/>
+      <c r="AC16" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="AD16" s="1">
         <f t="shared" si="7"/>
         <v>18.5</v>
@@ -2936,7 +2970,9 @@
       <c r="AB20" s="1">
         <v>2.1798000000000002</v>
       </c>
-      <c r="AC20" s="1"/>
+      <c r="AC20" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="AD20" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -3262,7 +3298,9 @@
       <c r="AB23" s="1">
         <v>35</v>
       </c>
-      <c r="AC23" s="1"/>
+      <c r="AC23" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="AD23" s="1">
         <f t="shared" si="7"/>
         <v>11.22</v>
@@ -4801,8 +4839,8 @@
       <c r="H38" s="1">
         <v>60</v>
       </c>
-      <c r="I38" s="1">
-        <v>6453</v>
+      <c r="I38" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1">
@@ -4858,7 +4896,9 @@
       <c r="AB38" s="1">
         <v>45.4</v>
       </c>
-      <c r="AC38" s="1"/>
+      <c r="AC38" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="AD38" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -4907,8 +4947,8 @@
       <c r="H39" s="1">
         <v>60</v>
       </c>
-      <c r="I39" s="1">
-        <v>6454</v>
+      <c r="I39" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1">
@@ -4967,7 +5007,9 @@
       <c r="AB39" s="1">
         <v>33.4</v>
       </c>
-      <c r="AC39" s="1"/>
+      <c r="AC39" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="AD39" s="1">
         <f t="shared" si="7"/>
         <v>19.900000000000002</v>
@@ -5016,8 +5058,8 @@
       <c r="H40" s="1">
         <v>45</v>
       </c>
-      <c r="I40" s="1">
-        <v>6459</v>
+      <c r="I40" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1">
@@ -5076,7 +5118,9 @@
       <c r="AB40" s="1">
         <v>5.8</v>
       </c>
-      <c r="AC40" s="1"/>
+      <c r="AC40" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="AD40" s="1">
         <f t="shared" si="7"/>
         <v>7.4</v>
@@ -7957,7 +8001,9 @@
       <c r="AB67" s="1">
         <v>9.4</v>
       </c>
-      <c r="AC67" s="1"/>
+      <c r="AC67" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="AD67" s="1">
         <f t="shared" si="7"/>
         <v>4.75</v>
@@ -8393,7 +8439,7 @@
       </c>
       <c r="AC71" s="1"/>
       <c r="AD71" s="1">
-        <f t="shared" ref="AD71:AD106" si="24">G71*T71</f>
+        <f t="shared" ref="AD71:AD109" si="24">G71*T71</f>
         <v>0</v>
       </c>
       <c r="AE71" s="1"/>
@@ -12155,15 +12201,23 @@
       <c r="AV106" s="1"/>
     </row>
     <row r="107" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
+      <c r="A107" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
-      <c r="G107" s="7"/>
+      <c r="G107" s="7">
+        <v>0.1</v>
+      </c>
       <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
+      <c r="I107" s="1">
+        <v>7647</v>
+      </c>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -12172,19 +12226,40 @@
       <c r="O107" s="1"/>
       <c r="P107" s="1"/>
       <c r="Q107" s="1"/>
-      <c r="R107" s="1"/>
+      <c r="R107" s="1">
+        <v>0</v>
+      </c>
       <c r="S107" s="1"/>
-      <c r="T107" s="1"/>
+      <c r="T107" s="1">
+        <v>500</v>
+      </c>
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
-      <c r="W107" s="1"/>
-      <c r="X107" s="1"/>
-      <c r="Y107" s="1"/>
-      <c r="Z107" s="1"/>
-      <c r="AA107" s="1"/>
-      <c r="AB107" s="1"/>
-      <c r="AC107" s="1"/>
-      <c r="AD107" s="1"/>
+      <c r="W107" s="1">
+        <v>0</v>
+      </c>
+      <c r="X107" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD107" s="1">
+        <f t="shared" si="24"/>
+        <v>50</v>
+      </c>
       <c r="AE107" s="1"/>
       <c r="AF107" s="1"/>
       <c r="AG107" s="1"/>
@@ -12205,15 +12280,23 @@
       <c r="AV107" s="1"/>
     </row>
     <row r="108" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A108" s="1"/>
-      <c r="B108" s="1"/>
+      <c r="A108" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
-      <c r="G108" s="7"/>
+      <c r="G108" s="7">
+        <v>0.1</v>
+      </c>
       <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
+      <c r="I108" s="1">
+        <v>7651</v>
+      </c>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -12222,19 +12305,40 @@
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
       <c r="Q108" s="1"/>
-      <c r="R108" s="1"/>
+      <c r="R108" s="1">
+        <v>0</v>
+      </c>
       <c r="S108" s="1"/>
-      <c r="T108" s="1"/>
+      <c r="T108" s="1">
+        <v>500</v>
+      </c>
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
-      <c r="W108" s="1"/>
-      <c r="X108" s="1"/>
-      <c r="Y108" s="1"/>
-      <c r="Z108" s="1"/>
-      <c r="AA108" s="1"/>
-      <c r="AB108" s="1"/>
-      <c r="AC108" s="1"/>
-      <c r="AD108" s="1"/>
+      <c r="W108" s="1">
+        <v>0</v>
+      </c>
+      <c r="X108" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB108" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC108" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD108" s="1">
+        <f t="shared" si="24"/>
+        <v>50</v>
+      </c>
       <c r="AE108" s="1"/>
       <c r="AF108" s="1"/>
       <c r="AG108" s="1"/>
@@ -12255,15 +12359,23 @@
       <c r="AV108" s="1"/>
     </row>
     <row r="109" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
+      <c r="A109" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
-      <c r="G109" s="7"/>
+      <c r="G109" s="7">
+        <v>1</v>
+      </c>
       <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
+      <c r="I109" s="1">
+        <v>7299</v>
+      </c>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
@@ -12272,19 +12384,40 @@
       <c r="O109" s="1"/>
       <c r="P109" s="1"/>
       <c r="Q109" s="1"/>
-      <c r="R109" s="1"/>
+      <c r="R109" s="1">
+        <v>0</v>
+      </c>
       <c r="S109" s="1"/>
-      <c r="T109" s="1"/>
+      <c r="T109" s="1">
+        <v>50</v>
+      </c>
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
-      <c r="W109" s="1"/>
-      <c r="X109" s="1"/>
-      <c r="Y109" s="1"/>
-      <c r="Z109" s="1"/>
-      <c r="AA109" s="1"/>
-      <c r="AB109" s="1"/>
-      <c r="AC109" s="1"/>
-      <c r="AD109" s="1"/>
+      <c r="W109" s="1">
+        <v>0</v>
+      </c>
+      <c r="X109" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC109" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD109" s="1">
+        <f t="shared" si="24"/>
+        <v>50</v>
+      </c>
       <c r="AE109" s="1"/>
       <c r="AF109" s="1"/>
       <c r="AG109" s="1"/>
@@ -31855,7 +31988,7 @@
       <c r="AV500" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AD106" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AD109" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
